--- a/outputs/план_поставки_КОРОТИЧ_6складов_30.07.2026.xlsx
+++ b/outputs/план_поставки_КОРОТИЧ_6складов_30.07.2026.xlsx
@@ -624,7 +624,7 @@
         <v>0.5</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1878</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="6">
@@ -664,7 +664,7 @@
         <v>0.4</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>897</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -704,7 +704,7 @@
         <v>0.4</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>890</v>
+        <v>903</v>
       </c>
     </row>
     <row r="8">
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>616</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9">
@@ -784,7 +784,7 @@
         <v>0.6</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>433</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10">
@@ -824,7 +824,7 @@
         <v>0.5</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>336</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11">
@@ -864,7 +864,7 @@
         <v>0.2</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12">
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>67</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13">
@@ -944,7 +944,7 @@
         <v>0.3</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14">
@@ -984,7 +984,7 @@
         <v>0.8</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>181</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15">
@@ -1024,7 +1024,7 @@
         <v>0.5</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16">
@@ -1064,7 +1064,7 @@
         <v>0.6</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17">
@@ -1104,7 +1104,7 @@
         <v>0.3</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>166</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18">
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19">
@@ -1184,7 +1184,7 @@
         <v>1.2</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
@@ -1224,7 +1224,7 @@
         <v>0.8</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21">
@@ -1264,7 +1264,7 @@
         <v>0.4</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22">
@@ -1304,7 +1304,7 @@
         <v>0.3</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23">
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
@@ -1384,7 +1384,7 @@
         <v>0.5</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
@@ -1424,7 +1424,7 @@
         <v>0.4</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>97</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27">
@@ -1504,7 +1504,7 @@
         <v>0.1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28">
@@ -1544,7 +1544,7 @@
         <v>2.6</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
@@ -1624,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
@@ -1664,7 +1664,7 @@
         <v>0.2</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32">
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33">
@@ -1744,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34">
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35">
@@ -1824,7 +1824,7 @@
         <v>0.6</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
@@ -1864,7 +1864,7 @@
         <v>2</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37">
@@ -1904,7 +1904,7 @@
         <v>0.1</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38">
@@ -1984,7 +1984,7 @@
         <v>0.5</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40">
@@ -2024,7 +2024,7 @@
         <v>0.8</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
@@ -2064,7 +2064,7 @@
         <v>1.8</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42">
@@ -2144,7 +2144,7 @@
         <v>0.5</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
@@ -2184,7 +2184,7 @@
         <v>0.3</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45">
@@ -2224,7 +2224,7 @@
         <v>1.7</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47">
@@ -2304,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48">
@@ -2344,7 +2344,7 @@
         <v>0.6</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50">
@@ -2424,7 +2424,7 @@
         <v>0.8</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51">
@@ -2464,7 +2464,7 @@
         <v>4.3</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -2544,7 +2544,7 @@
         <v>3</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
@@ -2584,7 +2584,7 @@
         <v>0.5</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55">
@@ -2624,7 +2624,7 @@
         <v>0.3</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56">
@@ -2664,7 +2664,7 @@
         <v>0.3</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57">
@@ -2704,7 +2704,7 @@
         <v>0.4</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58">
@@ -2744,7 +2744,7 @@
         <v>1.9</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59">
@@ -2784,7 +2784,7 @@
         <v>2.6</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60">
@@ -2824,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
@@ -2864,7 +2864,7 @@
         <v>3.7</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
@@ -2904,7 +2904,7 @@
         <v>1.6</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
@@ -2944,7 +2944,7 @@
         <v>0.2</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
@@ -2984,7 +2984,7 @@
         <v>2.2</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -3024,7 +3024,7 @@
         <v>0.1</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66">
@@ -3064,7 +3064,7 @@
         <v>0.6</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67">
@@ -3104,7 +3104,7 @@
         <v>2.6</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
@@ -3144,7 +3144,7 @@
         <v>1.4</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69">
@@ -3184,7 +3184,7 @@
         <v>0.2</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70">
@@ -3224,7 +3224,7 @@
         <v>0.1</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71">
@@ -3264,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
@@ -3304,7 +3304,7 @@
         <v>0.9</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73">
@@ -3344,7 +3344,7 @@
         <v>2.6</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
@@ -3384,7 +3384,7 @@
         <v>1.7</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75">
@@ -3424,7 +3424,7 @@
         <v>0.2</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76">
@@ -3464,7 +3464,7 @@
         <v>0.9</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
@@ -3504,7 +3504,7 @@
         <v>1.7</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
@@ -3544,7 +3544,7 @@
         <v>1.8</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
@@ -3584,7 +3584,7 @@
         <v>4.9</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
@@ -3624,7 +3624,7 @@
         <v>0.6</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -3664,7 +3664,7 @@
         <v>2.5</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
@@ -3704,7 +3704,7 @@
         <v>0.1</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
@@ -3784,7 +3784,7 @@
         <v>1.3</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
@@ -3824,7 +3824,7 @@
         <v>0.7</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
@@ -3864,7 +3864,7 @@
         <v>10.3</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
@@ -3904,7 +3904,7 @@
         <v>0.4</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88">
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89">
@@ -3984,7 +3984,7 @@
         <v>7.4</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90">
@@ -4024,7 +4024,7 @@
         <v>6</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91">
@@ -4064,7 +4064,7 @@
         <v>0.1</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
@@ -4104,7 +4104,7 @@
         <v>1.4</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93">
@@ -4184,7 +4184,7 @@
         <v>1.7</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
@@ -4224,7 +4224,7 @@
         <v>3.5</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
@@ -4384,7 +4384,7 @@
         <v>14.9</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -4424,7 +4424,7 @@
         <v>3.6</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -4464,7 +4464,7 @@
         <v>0.1</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102">
@@ -4504,7 +4504,7 @@
         <v>0.2</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
@@ -4544,7 +4544,7 @@
         <v>1.5</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
@@ -4584,7 +4584,7 @@
         <v>1.6</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -4624,7 +4624,7 @@
         <v>0.4</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
@@ -4664,7 +4664,7 @@
         <v>1.2</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -4704,7 +4704,7 @@
         <v>6.9</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -4784,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
@@ -4824,7 +4824,7 @@
         <v>1.9</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -4864,7 +4864,7 @@
         <v>4.2</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -4904,7 +4904,7 @@
         <v>14.5</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -4944,7 +4944,7 @@
         <v>4.1</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
@@ -4984,7 +4984,7 @@
         <v>4.3</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -5024,7 +5024,7 @@
         <v>26.3</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -5064,7 +5064,7 @@
         <v>6.2</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -5104,7 +5104,7 @@
         <v>0</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118">
@@ -5704,7 +5704,7 @@
         <v>72</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -6152,7 +6152,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>К поставке = спрос/мес − текущий остаток на складе. Питер/Краснодар/Новосибирск сейчас пустые (остаток 0). Новосибирск = спрос Сибирского ФО (10,1%).</t>
+          <t>К поставке = спрос/мес − текущий остаток. Питер = спрос СЗ ФО (8,4%), Новосибирск = Сибирский ФО (10,1%) — склады пустые. Краснодар пустой. Екб/Казань/Владимир — довоз разницы.</t>
         </is>
       </c>
     </row>
@@ -6311,10 +6311,10 @@
         <v>3355</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>134</v>
+        <v>283</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>134</v>
+        <v>283</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>709</v>
@@ -6347,7 +6347,7 @@
         <v>181</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>1878</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7">
@@ -6376,10 +6376,10 @@
         <v>1859</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>183</v>
@@ -6412,7 +6412,7 @@
         <v>129</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>897</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8">
@@ -6441,10 +6441,10 @@
         <v>1459</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>302</v>
@@ -6477,7 +6477,7 @@
         <v>303</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>890</v>
+        <v>903</v>
       </c>
     </row>
     <row r="9">
@@ -6506,10 +6506,10 @@
         <v>955</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>227</v>
@@ -6542,7 +6542,7 @@
         <v>175</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>616</v>
+        <v>664</v>
       </c>
     </row>
     <row r="10">
@@ -6571,10 +6571,10 @@
         <v>875</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>136</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>433</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11">
@@ -6636,10 +6636,10 @@
         <v>754</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>139</v>
@@ -6672,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>336</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12">
@@ -6701,10 +6701,10 @@
         <v>648</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>103</v>
@@ -6737,7 +6737,7 @@
         <v>61</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13">
@@ -6766,10 +6766,10 @@
         <v>507</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>1</v>
@@ -6802,7 +6802,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>67</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14">
@@ -6831,10 +6831,10 @@
         <v>428</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>66</v>
@@ -6867,7 +6867,7 @@
         <v>28</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15">
@@ -6896,10 +6896,10 @@
         <v>406</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>75</v>
@@ -6932,7 +6932,7 @@
         <v>13</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>181</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16">
@@ -6961,10 +6961,10 @@
         <v>396</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>67</v>
@@ -6997,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17">
@@ -7026,10 +7026,10 @@
         <v>395</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>55</v>
@@ -7062,7 +7062,7 @@
         <v>59</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18">
@@ -7091,10 +7091,10 @@
         <v>364</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>32</v>
@@ -7127,7 +7127,7 @@
         <v>42</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>166</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19">
@@ -7156,10 +7156,10 @@
         <v>334</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>100</v>
@@ -7192,7 +7192,7 @@
         <v>36</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20">
@@ -7221,10 +7221,10 @@
         <v>264</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>47</v>
@@ -7257,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21">
@@ -7286,10 +7286,10 @@
         <v>244</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>39</v>
@@ -7322,7 +7322,7 @@
         <v>47</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22">
@@ -7351,10 +7351,10 @@
         <v>211</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>49</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23">
@@ -7416,10 +7416,10 @@
         <v>183</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>23</v>
@@ -7452,7 +7452,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24">
@@ -7481,10 +7481,10 @@
         <v>178</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>33</v>
@@ -7517,7 +7517,7 @@
         <v>47</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
@@ -7546,10 +7546,10 @@
         <v>174</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>28</v>
@@ -7582,7 +7582,7 @@
         <v>12</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
@@ -7611,10 +7611,10 @@
         <v>173</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>2</v>
@@ -7647,7 +7647,7 @@
         <v>17</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
@@ -7676,10 +7676,10 @@
         <v>173</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>5</v>
@@ -7712,7 +7712,7 @@
         <v>25</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>97</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28">
@@ -7741,10 +7741,10 @@
         <v>163</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>23</v>
@@ -7777,7 +7777,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29">
@@ -7806,10 +7806,10 @@
         <v>149</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>39</v>
@@ -7842,7 +7842,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30">
@@ -7936,10 +7936,10 @@
         <v>148</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>27</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
@@ -8001,10 +8001,10 @@
         <v>142</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>15</v>
@@ -8037,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33">
@@ -8066,10 +8066,10 @@
         <v>135</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>1</v>
@@ -8102,7 +8102,7 @@
         <v>37</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34">
@@ -8131,10 +8131,10 @@
         <v>122</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>17</v>
@@ -8167,7 +8167,7 @@
         <v>24</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
@@ -8196,10 +8196,10 @@
         <v>122</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>22</v>
@@ -8232,7 +8232,7 @@
         <v>33</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36">
@@ -8261,10 +8261,10 @@
         <v>120</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>35</v>
@@ -8297,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="6" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37">
@@ -8326,10 +8326,10 @@
         <v>119</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>45</v>
@@ -8362,7 +8362,7 @@
         <v>0</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38">
@@ -8391,10 +8391,10 @@
         <v>119</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>10</v>
@@ -8427,7 +8427,7 @@
         <v>11</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39">
@@ -8521,10 +8521,10 @@
         <v>113</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>17</v>
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="6" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41">
@@ -8586,10 +8586,10 @@
         <v>112</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>1</v>
@@ -8622,7 +8622,7 @@
         <v>20</v>
       </c>
       <c r="S41" s="6" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -8651,10 +8651,10 @@
         <v>98</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>17</v>
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="6" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43">
@@ -8781,10 +8781,10 @@
         <v>94</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>13</v>
@@ -8817,7 +8817,7 @@
         <v>0</v>
       </c>
       <c r="S44" s="6" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45">
@@ -8846,10 +8846,10 @@
         <v>90</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>18</v>
@@ -8882,7 +8882,7 @@
         <v>17</v>
       </c>
       <c r="S45" s="6" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46">
@@ -8911,10 +8911,10 @@
         <v>89</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>0</v>
@@ -8947,7 +8947,7 @@
         <v>16</v>
       </c>
       <c r="S46" s="6" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47">
@@ -8976,10 +8976,10 @@
         <v>87</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>44</v>
@@ -9012,7 +9012,7 @@
         <v>0</v>
       </c>
       <c r="S47" s="6" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48">
@@ -9041,10 +9041,10 @@
         <v>86</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H48" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>1</v>
@@ -9077,7 +9077,7 @@
         <v>58</v>
       </c>
       <c r="S48" s="6" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49">
@@ -9106,10 +9106,10 @@
         <v>84</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>2</v>
@@ -9142,7 +9142,7 @@
         <v>2</v>
       </c>
       <c r="S49" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
@@ -9171,10 +9171,10 @@
         <v>82</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I50" s="5" t="n">
         <v>3</v>
@@ -9207,7 +9207,7 @@
         <v>74</v>
       </c>
       <c r="S50" s="6" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51">
@@ -9236,10 +9236,10 @@
         <v>75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I51" s="5" t="n">
         <v>15</v>
@@ -9272,7 +9272,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="6" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52">
@@ -9301,10 +9301,10 @@
         <v>73</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>17</v>
@@ -9337,7 +9337,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
@@ -9431,10 +9431,10 @@
         <v>71</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H54" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>8</v>
@@ -9467,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="S54" s="6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
@@ -9496,10 +9496,10 @@
         <v>71</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H55" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I55" s="5" t="n">
         <v>15</v>
@@ -9532,7 +9532,7 @@
         <v>0</v>
       </c>
       <c r="S55" s="6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56">
@@ -9561,10 +9561,10 @@
         <v>70</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H56" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I56" s="5" t="n">
         <v>1</v>
@@ -9597,7 +9597,7 @@
         <v>8</v>
       </c>
       <c r="S56" s="6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
@@ -9626,10 +9626,10 @@
         <v>67</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H57" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I57" s="5" t="n">
         <v>11</v>
@@ -9662,7 +9662,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="6" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58">
@@ -9691,10 +9691,10 @@
         <v>66</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H58" s="11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I58" s="5" t="n">
         <v>2</v>
@@ -9727,7 +9727,7 @@
         <v>8</v>
       </c>
       <c r="S58" s="6" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59">
@@ -9756,10 +9756,10 @@
         <v>59</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H59" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I59" s="5" t="n">
         <v>12</v>
@@ -9792,7 +9792,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60">
@@ -9821,10 +9821,10 @@
         <v>59</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H60" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I60" s="5" t="n">
         <v>12</v>
@@ -9857,7 +9857,7 @@
         <v>0</v>
       </c>
       <c r="S60" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61">
@@ -9886,10 +9886,10 @@
         <v>55</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I61" s="5" t="n">
         <v>1</v>
@@ -9922,7 +9922,7 @@
         <v>7</v>
       </c>
       <c r="S61" s="6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
@@ -9951,10 +9951,10 @@
         <v>54</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H62" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I62" s="5" t="n">
         <v>2</v>
@@ -9987,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
@@ -10016,10 +10016,10 @@
         <v>53</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H63" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I63" s="5" t="n">
         <v>5</v>
@@ -10052,7 +10052,7 @@
         <v>9</v>
       </c>
       <c r="S63" s="6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -10081,10 +10081,10 @@
         <v>53</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H64" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I64" s="5" t="n">
         <v>2</v>
@@ -10117,7 +10117,7 @@
         <v>7</v>
       </c>
       <c r="S64" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
@@ -10146,10 +10146,10 @@
         <v>51</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H65" s="11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I65" s="5" t="n">
         <v>0</v>
@@ -10182,7 +10182,7 @@
         <v>0</v>
       </c>
       <c r="S65" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -10211,10 +10211,10 @@
         <v>51</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H66" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I66" s="5" t="n">
         <v>8</v>
@@ -10247,7 +10247,7 @@
         <v>6</v>
       </c>
       <c r="S66" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67">
@@ -10276,10 +10276,10 @@
         <v>49</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H67" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I67" s="5" t="n">
         <v>0</v>
@@ -10312,7 +10312,7 @@
         <v>9</v>
       </c>
       <c r="S67" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68">
@@ -10341,10 +10341,10 @@
         <v>47</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H68" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I68" s="5" t="n">
         <v>12</v>
@@ -10377,7 +10377,7 @@
         <v>0</v>
       </c>
       <c r="S68" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69">
@@ -10406,10 +10406,10 @@
         <v>45</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H69" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I69" s="5" t="n">
         <v>8</v>
@@ -10442,7 +10442,7 @@
         <v>0</v>
       </c>
       <c r="S69" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
@@ -10471,10 +10471,10 @@
         <v>45</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H70" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I70" s="5" t="n">
         <v>4</v>
@@ -10507,7 +10507,7 @@
         <v>11</v>
       </c>
       <c r="S70" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71">
@@ -10536,10 +10536,10 @@
         <v>44</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H71" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I71" s="5" t="n">
         <v>7</v>
@@ -10572,7 +10572,7 @@
         <v>6</v>
       </c>
       <c r="S71" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72">
@@ -10601,10 +10601,10 @@
         <v>43</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H72" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I72" s="5" t="n">
         <v>12</v>
@@ -10637,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73">
@@ -10666,10 +10666,10 @@
         <v>42</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H73" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I73" s="5" t="n">
         <v>5</v>
@@ -10702,7 +10702,7 @@
         <v>3</v>
       </c>
       <c r="S73" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74">
@@ -10731,10 +10731,10 @@
         <v>39</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H74" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I74" s="5" t="n">
         <v>2</v>
@@ -10767,7 +10767,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
@@ -10796,10 +10796,10 @@
         <v>39</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75" s="5" t="n">
         <v>9</v>
@@ -10832,7 +10832,7 @@
         <v>6</v>
       </c>
       <c r="S75" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76">
@@ -10861,10 +10861,10 @@
         <v>39</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H76" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I76" s="5" t="n">
         <v>0</v>
@@ -10897,7 +10897,7 @@
         <v>4</v>
       </c>
       <c r="S76" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77">
@@ -10926,10 +10926,10 @@
         <v>36</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H77" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I77" s="5" t="n">
         <v>3</v>
@@ -10962,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -10991,10 +10991,10 @@
         <v>35</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H78" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I78" s="5" t="n">
         <v>5</v>
@@ -11027,7 +11027,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79">
@@ -11056,10 +11056,10 @@
         <v>35</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H79" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>1</v>
@@ -11092,7 +11092,7 @@
         <v>0</v>
       </c>
       <c r="S79" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
@@ -11121,10 +11121,10 @@
         <v>34</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H80" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I80" s="5" t="n">
         <v>3</v>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="S80" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
@@ -11186,10 +11186,10 @@
         <v>34</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H81" s="11" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>0</v>
@@ -11222,7 +11222,7 @@
         <v>1</v>
       </c>
       <c r="S81" s="6" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -11251,10 +11251,10 @@
         <v>33</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H82" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I82" s="5" t="n">
         <v>2</v>
@@ -11287,7 +11287,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -11316,10 +11316,10 @@
         <v>33</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H83" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I83" s="5" t="n">
         <v>0</v>
@@ -11352,7 +11352,7 @@
         <v>6</v>
       </c>
       <c r="S83" s="6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
@@ -11446,10 +11446,10 @@
         <v>31</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H85" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I85" s="5" t="n">
         <v>3</v>
@@ -11482,7 +11482,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
@@ -11511,10 +11511,10 @@
         <v>30</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H86" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I86" s="5" t="n">
         <v>0</v>
@@ -11547,7 +11547,7 @@
         <v>0</v>
       </c>
       <c r="S86" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
@@ -11576,10 +11576,10 @@
         <v>29</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H87" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I87" s="5" t="n">
         <v>7</v>
@@ -11612,7 +11612,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
@@ -11641,10 +11641,10 @@
         <v>29</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H88" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I88" s="5" t="n">
         <v>3</v>
@@ -11677,7 +11677,7 @@
         <v>5</v>
       </c>
       <c r="S88" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89">
@@ -11706,10 +11706,10 @@
         <v>28</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H89" s="11" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I89" s="5" t="n">
         <v>0</v>
@@ -11742,7 +11742,7 @@
         <v>8</v>
       </c>
       <c r="S89" s="6" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
@@ -11771,10 +11771,10 @@
         <v>27</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H90" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I90" s="5" t="n">
         <v>6</v>
@@ -11807,7 +11807,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
@@ -11836,10 +11836,10 @@
         <v>27</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H91" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I91" s="5" t="n">
         <v>7</v>
@@ -11872,7 +11872,7 @@
         <v>6</v>
       </c>
       <c r="S91" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92">
@@ -11901,10 +11901,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H92" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I92" s="5" t="n">
         <v>0</v>
@@ -11937,7 +11937,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -11966,10 +11966,10 @@
         <v>25</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H93" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" s="5" t="n">
         <v>0</v>
@@ -12002,7 +12002,7 @@
         <v>11</v>
       </c>
       <c r="S93" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94">
@@ -12096,10 +12096,10 @@
         <v>24</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I95" s="5" t="n">
         <v>3</v>
@@ -12132,7 +12132,7 @@
         <v>2</v>
       </c>
       <c r="S95" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
@@ -12161,10 +12161,10 @@
         <v>20</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H96" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I96" s="5" t="n">
         <v>3</v>
@@ -12197,7 +12197,7 @@
         <v>0</v>
       </c>
       <c r="S96" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97">
@@ -12421,10 +12421,10 @@
         <v>17</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" s="5" t="n">
         <v>0</v>
@@ -12457,7 +12457,7 @@
         <v>0</v>
       </c>
       <c r="S100" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -12486,10 +12486,10 @@
         <v>16</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I101" s="5" t="n">
         <v>2</v>
@@ -12522,7 +12522,7 @@
         <v>0</v>
       </c>
       <c r="S101" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -12551,10 +12551,10 @@
         <v>16</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" s="5" t="n">
         <v>3</v>
@@ -12587,7 +12587,7 @@
         <v>2</v>
       </c>
       <c r="S102" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">
@@ -12616,10 +12616,10 @@
         <v>16</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" s="5" t="n">
         <v>0</v>
@@ -12652,7 +12652,7 @@
         <v>0</v>
       </c>
       <c r="S103" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
@@ -12681,10 +12681,10 @@
         <v>15</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" s="5" t="n">
         <v>3</v>
@@ -12717,7 +12717,7 @@
         <v>0</v>
       </c>
       <c r="S104" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
@@ -12746,10 +12746,10 @@
         <v>14</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" s="5" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -12811,10 +12811,10 @@
         <v>14</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" s="5" t="n">
         <v>1</v>
@@ -12847,7 +12847,7 @@
         <v>2</v>
       </c>
       <c r="S106" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -12876,10 +12876,10 @@
         <v>13</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107" s="5" t="n">
         <v>0</v>
@@ -12912,7 +12912,7 @@
         <v>0</v>
       </c>
       <c r="S107" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -12941,10 +12941,10 @@
         <v>12</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H108" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I108" s="5" t="n">
         <v>1</v>
@@ -12977,7 +12977,7 @@
         <v>0</v>
       </c>
       <c r="S108" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -13071,10 +13071,10 @@
         <v>11</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H110" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I110" s="5" t="n">
         <v>0</v>
@@ -13107,7 +13107,7 @@
         <v>0</v>
       </c>
       <c r="S110" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
@@ -13136,10 +13136,10 @@
         <v>10</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" s="5" t="n">
         <v>1</v>
@@ -13172,7 +13172,7 @@
         <v>0</v>
       </c>
       <c r="S111" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -13201,10 +13201,10 @@
         <v>8</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" s="5" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -13266,10 +13266,10 @@
         <v>8</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" s="5" t="n">
         <v>1</v>
@@ -13302,7 +13302,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -13331,10 +13331,10 @@
         <v>8</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" s="5" t="n">
         <v>2</v>
@@ -13367,7 +13367,7 @@
         <v>0</v>
       </c>
       <c r="S114" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
@@ -13396,10 +13396,10 @@
         <v>7</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" s="5" t="n">
         <v>0</v>
@@ -13432,7 +13432,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -13461,10 +13461,10 @@
         <v>6</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" s="5" t="n">
         <v>0</v>
@@ -13497,7 +13497,7 @@
         <v>1</v>
       </c>
       <c r="S116" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -13526,10 +13526,10 @@
         <v>6</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" s="5" t="n">
         <v>1</v>
@@ -13562,7 +13562,7 @@
         <v>0</v>
       </c>
       <c r="S117" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -13591,10 +13591,10 @@
         <v>6</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="5" t="n">
         <v>4</v>
@@ -13627,7 +13627,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119">
@@ -14566,10 +14566,10 @@
         <v>2</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="5" t="n">
         <v>0</v>
@@ -14602,7 +14602,7 @@
         <v>0</v>
       </c>
       <c r="S133" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -15262,10 +15262,10 @@
         </is>
       </c>
       <c r="G144" s="13" t="n">
-        <v>1006</v>
+        <v>1627</v>
       </c>
       <c r="H144" s="13" t="n">
-        <v>1006</v>
+        <v>1627</v>
       </c>
       <c r="I144" s="13" t="n">
         <v>3051</v>
@@ -15298,7 +15298,7 @@
         <v>1660</v>
       </c>
       <c r="S144" s="13" t="n">
-        <v>9527</v>
+        <v>10148</v>
       </c>
     </row>
   </sheetData>
@@ -15334,7 +15334,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15378,17 +15378,17 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1006</v>
+        <v>1627</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1006</v>
+        <v>1627</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>склад пустой — везём весь спрос</t>
+          <t>нет своего запаса — спрос Северо-Западного ФО (8,4%)</t>
         </is>
       </c>
     </row>
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>11483</v>
+        <v>12104</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>5267</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>9527</v>
+        <v>10148</v>
       </c>
       <c r="E10" s="14" t="inlineStr"/>
     </row>

--- a/outputs/план_поставки_КОРОТИЧ_6складов_30.07.2026.xlsx
+++ b/outputs/план_поставки_КОРОТИЧ_6складов_30.07.2026.xlsx
@@ -624,7 +624,7 @@
         <v>0.5</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>2027</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="6">
@@ -664,7 +664,7 @@
         <v>0.4</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>953</v>
+        <v>973</v>
       </c>
     </row>
     <row r="7">
@@ -704,7 +704,7 @@
         <v>0.4</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>903</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>664</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -784,7 +784,7 @@
         <v>0.6</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>450</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -824,7 +824,7 @@
         <v>0.5</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>364</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -864,7 +864,7 @@
         <v>0.2</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>360</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12">
@@ -904,7 +904,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>109</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -944,7 +944,7 @@
         <v>0.3</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>230</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14">
@@ -984,7 +984,7 @@
         <v>0.8</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>200</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15">
@@ -1024,7 +1024,7 @@
         <v>0.5</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>223</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16">
@@ -1064,7 +1064,7 @@
         <v>0.6</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>229</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17">
@@ -1104,7 +1104,7 @@
         <v>0.3</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>196</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18">
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>246</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19">
@@ -1184,7 +1184,7 @@
         <v>1.2</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>123</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
@@ -1224,7 +1224,7 @@
         <v>0.8</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21">
@@ -1264,7 +1264,7 @@
         <v>0.4</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>105</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22">
@@ -1304,7 +1304,7 @@
         <v>0.3</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>123</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
@@ -1384,7 +1384,7 @@
         <v>0.5</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25">
@@ -1424,7 +1424,7 @@
         <v>0.4</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
@@ -1504,7 +1504,7 @@
         <v>0.1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28">
@@ -1544,7 +1544,7 @@
         <v>2.6</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29">
@@ -1624,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
@@ -1664,7 +1664,7 @@
         <v>0.2</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32">
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33">
@@ -1744,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35">
@@ -1824,7 +1824,7 @@
         <v>0.6</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36">
@@ -1864,7 +1864,7 @@
         <v>2</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37">
@@ -1904,7 +1904,7 @@
         <v>0.1</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
@@ -1944,7 +1944,7 @@
         <v>0.2</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39">
@@ -1984,7 +1984,7 @@
         <v>0.5</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -2024,7 +2024,7 @@
         <v>0.8</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41">
@@ -2064,7 +2064,7 @@
         <v>1.8</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42">
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43">
@@ -2144,7 +2144,7 @@
         <v>0.5</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
@@ -2184,7 +2184,7 @@
         <v>0.3</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -2224,7 +2224,7 @@
         <v>1.7</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -2304,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48">
@@ -2344,7 +2344,7 @@
         <v>0.6</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50">
@@ -2424,7 +2424,7 @@
         <v>0.8</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51">
@@ -2464,7 +2464,7 @@
         <v>4.3</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
@@ -2504,7 +2504,7 @@
         <v>0.8</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
@@ -2544,7 +2544,7 @@
         <v>3</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -2584,7 +2584,7 @@
         <v>0.5</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -2624,7 +2624,7 @@
         <v>0.3</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56">
@@ -2664,7 +2664,7 @@
         <v>0.3</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
@@ -2704,7 +2704,7 @@
         <v>0.4</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58">
@@ -2744,7 +2744,7 @@
         <v>1.9</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59">
@@ -2784,7 +2784,7 @@
         <v>2.6</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60">
@@ -2824,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -2864,7 +2864,7 @@
         <v>3.7</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
@@ -2904,7 +2904,7 @@
         <v>1.6</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
@@ -2944,7 +2944,7 @@
         <v>0.2</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
@@ -2984,7 +2984,7 @@
         <v>2.2</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
@@ -3024,7 +3024,7 @@
         <v>0.1</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66">
@@ -3064,7 +3064,7 @@
         <v>0.6</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67">
@@ -3104,7 +3104,7 @@
         <v>2.6</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
@@ -3144,7 +3144,7 @@
         <v>1.4</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
@@ -3184,7 +3184,7 @@
         <v>0.2</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70">
@@ -3224,7 +3224,7 @@
         <v>0.1</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
@@ -3264,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
@@ -3304,7 +3304,7 @@
         <v>0.9</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
@@ -3344,7 +3344,7 @@
         <v>2.6</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
@@ -3384,7 +3384,7 @@
         <v>1.7</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75">
@@ -3424,7 +3424,7 @@
         <v>0.2</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76">
@@ -3464,7 +3464,7 @@
         <v>0.9</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77">
@@ -3504,7 +3504,7 @@
         <v>1.7</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78">
@@ -3544,7 +3544,7 @@
         <v>1.8</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79">
@@ -3584,7 +3584,7 @@
         <v>4.9</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
@@ -3624,7 +3624,7 @@
         <v>0.6</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81">
@@ -3664,7 +3664,7 @@
         <v>2.5</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
@@ -3704,7 +3704,7 @@
         <v>0.1</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -3744,7 +3744,7 @@
         <v>1.8</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84">
@@ -3784,7 +3784,7 @@
         <v>1.3</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
@@ -3824,7 +3824,7 @@
         <v>0.7</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
@@ -3864,7 +3864,7 @@
         <v>10.3</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87">
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89">
@@ -3984,7 +3984,7 @@
         <v>7.4</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90">
@@ -4024,7 +4024,7 @@
         <v>6</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91">
@@ -4064,7 +4064,7 @@
         <v>0.1</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92">
@@ -4104,7 +4104,7 @@
         <v>1.4</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
@@ -4144,7 +4144,7 @@
         <v>2.2</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -4184,7 +4184,7 @@
         <v>1.7</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -4224,7 +4224,7 @@
         <v>3.5</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
@@ -4304,7 +4304,7 @@
         <v>1.9</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
@@ -4344,7 +4344,7 @@
         <v>17.5</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
@@ -4384,7 +4384,7 @@
         <v>14.9</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -4504,7 +4504,7 @@
         <v>0.2</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">
@@ -4544,7 +4544,7 @@
         <v>1.5</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -4584,7 +4584,7 @@
         <v>1.6</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -4624,7 +4624,7 @@
         <v>0.4</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
@@ -4664,7 +4664,7 @@
         <v>1.2</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -4704,7 +4704,7 @@
         <v>6.9</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108">
@@ -4744,7 +4744,7 @@
         <v>0.5</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
@@ -4784,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
@@ -4824,7 +4824,7 @@
         <v>1.9</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
@@ -4864,7 +4864,7 @@
         <v>4.2</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -4984,7 +4984,7 @@
         <v>4.3</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
@@ -5104,7 +5104,7 @@
         <v>0</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
@@ -5184,7 +5184,7 @@
         <v>7.2</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -5264,7 +5264,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
@@ -5304,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="J122" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -5344,7 +5344,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -5384,7 +5384,7 @@
         <v>24</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -5424,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -5544,7 +5544,7 @@
         <v>13.3</v>
       </c>
       <c r="J128" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5704,7 +5704,7 @@
         <v>72</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -5744,7 +5744,7 @@
         <v>55</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -5784,7 +5784,7 @@
         <v>4</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -6104,7 +6104,7 @@
         <v>0</v>
       </c>
       <c r="J142" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6152,7 +6152,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>К поставке = спрос/мес − текущий остаток. Питер = спрос СЗ ФО (8,4%), Новосибирск = Сибирский ФО (10,1%) — склады пустые. Краснодар пустой. Екб/Казань/Владимир — довоз разницы.</t>
+          <t>Спрос склада = спрос его федерального округа: Питер=СЗ ФО, Краснодар=ЮФО, Новосибирск=Сибирский, Екб=УрФО, Казань=ПФО; Владимир=факт. К поставке = спрос − текущий остаток.</t>
         </is>
       </c>
     </row>
@@ -6317,10 +6317,10 @@
         <v>283</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>709</v>
+        <v>422</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>709</v>
+        <v>422</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>339</v>
@@ -6329,10 +6329,10 @@
         <v>339</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>650</v>
+        <v>227</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>507</v>
+        <v>84</v>
       </c>
       <c r="O6" s="5" t="n">
         <v>8</v>
@@ -6341,13 +6341,13 @@
         <v>8</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>404</v>
+        <v>470</v>
       </c>
       <c r="R6" s="11" t="n">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="S6" s="6" t="n">
-        <v>2027</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="7">
@@ -6382,10 +6382,10 @@
         <v>157</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>188</v>
@@ -6394,10 +6394,10 @@
         <v>188</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>286</v>
+        <v>126</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>286</v>
+        <v>126</v>
       </c>
       <c r="O7" s="5" t="n">
         <v>12</v>
@@ -6406,13 +6406,13 @@
         <v>10</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>129</v>
+        <v>258</v>
       </c>
       <c r="S7" s="6" t="n">
-        <v>953</v>
+        <v>973</v>
       </c>
     </row>
     <row r="8">
@@ -6447,10 +6447,10 @@
         <v>123</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>302</v>
+        <v>184</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>302</v>
+        <v>184</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>148</v>
@@ -6459,10 +6459,10 @@
         <v>148</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O8" s="5" t="n">
         <v>12</v>
@@ -6471,13 +6471,13 @@
         <v>12</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>332</v>
+        <v>204</v>
       </c>
       <c r="R8" s="11" t="n">
-        <v>303</v>
+        <v>175</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>903</v>
+        <v>643</v>
       </c>
     </row>
     <row r="9">
@@ -6512,10 +6512,10 @@
         <v>81</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>227</v>
+        <v>120</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>227</v>
+        <v>120</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>97</v>
@@ -6524,10 +6524,10 @@
         <v>97</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="O9" s="5" t="n">
         <v>2</v>
@@ -6536,13 +6536,13 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="R9" s="11" t="n">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>664</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10">
@@ -6577,10 +6577,10 @@
         <v>74</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>89</v>
@@ -6589,10 +6589,10 @@
         <v>89</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>179</v>
+        <v>59</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>151</v>
+        <v>31</v>
       </c>
       <c r="O10" s="5" t="n">
         <v>0</v>
@@ -6601,13 +6601,13 @@
         <v>0</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="R10" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S10" s="6" t="n">
-        <v>450</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11">
@@ -6642,10 +6642,10 @@
         <v>64</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>76</v>
@@ -6654,10 +6654,10 @@
         <v>76</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="O11" s="5" t="n">
         <v>4</v>
@@ -6666,13 +6666,13 @@
         <v>4</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="R11" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>364</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12">
@@ -6707,10 +6707,10 @@
         <v>55</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>66</v>
@@ -6719,10 +6719,10 @@
         <v>66</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="N12" s="11" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="O12" s="5" t="n">
         <v>1</v>
@@ -6731,13 +6731,13 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="R12" s="11" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>360</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -6772,10 +6772,10 @@
         <v>43</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="K13" s="5" t="n">
         <v>51</v>
@@ -6784,10 +6784,10 @@
         <v>51</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O13" s="5" t="n">
         <v>1</v>
@@ -6796,13 +6796,13 @@
         <v>1</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="R13" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>109</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -6837,10 +6837,10 @@
         <v>36</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>43</v>
@@ -6849,10 +6849,10 @@
         <v>43</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>2</v>
@@ -6861,13 +6861,13 @@
         <v>2</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="R14" s="11" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>230</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15">
@@ -6902,10 +6902,10 @@
         <v>34</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>41</v>
@@ -6914,10 +6914,10 @@
         <v>41</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O15" s="5" t="n">
         <v>1</v>
@@ -6926,13 +6926,13 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R15" s="11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>200</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16">
@@ -6967,10 +6967,10 @@
         <v>33</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>40</v>
@@ -6979,10 +6979,10 @@
         <v>40</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="N16" s="11" t="n">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O16" s="5" t="n">
         <v>0</v>
@@ -6991,13 +6991,13 @@
         <v>0</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="R16" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>223</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17">
@@ -7032,10 +7032,10 @@
         <v>33</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K17" s="5" t="n">
         <v>40</v>
@@ -7044,10 +7044,10 @@
         <v>40</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="N17" s="11" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="O17" s="5" t="n">
         <v>1</v>
@@ -7056,13 +7056,13 @@
         <v>1</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="R17" s="11" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>229</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18">
@@ -7097,10 +7097,10 @@
         <v>31</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>37</v>
@@ -7109,10 +7109,10 @@
         <v>37</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="N18" s="11" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="O18" s="5" t="n">
         <v>1</v>
@@ -7121,13 +7121,13 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="R18" s="11" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>196</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19">
@@ -7162,10 +7162,10 @@
         <v>28</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>34</v>
@@ -7174,10 +7174,10 @@
         <v>34</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="N19" s="11" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="O19" s="5" t="n">
         <v>2</v>
@@ -7186,13 +7186,13 @@
         <v>2</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="R19" s="11" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>246</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20">
@@ -7227,10 +7227,10 @@
         <v>22</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>27</v>
@@ -7239,10 +7239,10 @@
         <v>27</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="N20" s="11" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="O20" s="5" t="n">
         <v>0</v>
@@ -7251,13 +7251,13 @@
         <v>0</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="R20" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>123</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
@@ -7292,10 +7292,10 @@
         <v>21</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>25</v>
@@ -7304,10 +7304,10 @@
         <v>25</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N21" s="11" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O21" s="5" t="n">
         <v>1</v>
@@ -7316,13 +7316,13 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R21" s="11" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22">
@@ -7357,10 +7357,10 @@
         <v>18</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>21</v>
@@ -7369,10 +7369,10 @@
         <v>21</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="N22" s="11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O22" s="5" t="n">
         <v>0</v>
@@ -7381,13 +7381,13 @@
         <v>0</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="R22" s="11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>105</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23">
@@ -7434,10 +7434,10 @@
         <v>19</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="N23" s="11" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O23" s="5" t="n">
         <v>1</v>
@@ -7446,13 +7446,13 @@
         <v>1</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="R23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24">
@@ -7487,10 +7487,10 @@
         <v>15</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>18</v>
@@ -7499,10 +7499,10 @@
         <v>18</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N24" s="11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O24" s="5" t="n">
         <v>1</v>
@@ -7511,13 +7511,13 @@
         <v>1</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="R24" s="11" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>123</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25">
@@ -7552,10 +7552,10 @@
         <v>15</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>18</v>
@@ -7564,10 +7564,10 @@
         <v>18</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N25" s="11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O25" s="5" t="n">
         <v>0</v>
@@ -7576,13 +7576,13 @@
         <v>0</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="R25" s="11" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26">
@@ -7617,10 +7617,10 @@
         <v>15</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>17</v>
@@ -7629,10 +7629,10 @@
         <v>17</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N26" s="11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O26" s="5" t="n">
         <v>0</v>
@@ -7641,13 +7641,13 @@
         <v>0</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R26" s="11" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
@@ -7682,10 +7682,10 @@
         <v>15</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>17</v>
@@ -7694,10 +7694,10 @@
         <v>17</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N27" s="11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O27" s="5" t="n">
         <v>0</v>
@@ -7706,13 +7706,13 @@
         <v>0</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R27" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
@@ -7747,10 +7747,10 @@
         <v>14</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K28" s="5" t="n">
         <v>16</v>
@@ -7759,10 +7759,10 @@
         <v>16</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N28" s="11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O28" s="5" t="n">
         <v>1</v>
@@ -7771,13 +7771,13 @@
         <v>1</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R28" s="11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S28" s="6" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29">
@@ -7812,10 +7812,10 @@
         <v>13</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="K29" s="5" t="n">
         <v>15</v>
@@ -7824,10 +7824,10 @@
         <v>15</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N29" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O29" s="5" t="n">
         <v>0</v>
@@ -7836,13 +7836,13 @@
         <v>0</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R29" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30">
@@ -7877,10 +7877,10 @@
         <v>12</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J30" s="11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K30" s="5" t="n">
         <v>15</v>
@@ -7889,7 +7889,7 @@
         <v>15</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="N30" s="11" t="n">
         <v>0</v>
@@ -7901,10 +7901,10 @@
         <v>0</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R30" s="11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S30" s="6" t="n">
         <v>55</v>
@@ -7942,10 +7942,10 @@
         <v>12</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K31" s="5" t="n">
         <v>15</v>
@@ -7954,7 +7954,7 @@
         <v>15</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N31" s="11" t="n">
         <v>0</v>
@@ -7966,13 +7966,13 @@
         <v>2</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R31" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S31" s="6" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
@@ -8007,10 +8007,10 @@
         <v>12</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>14</v>
@@ -8019,10 +8019,10 @@
         <v>14</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N32" s="11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O32" s="5" t="n">
         <v>0</v>
@@ -8031,13 +8031,13 @@
         <v>0</v>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R32" s="11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S32" s="6" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33">
@@ -8072,10 +8072,10 @@
         <v>11</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K33" s="5" t="n">
         <v>14</v>
@@ -8084,10 +8084,10 @@
         <v>14</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N33" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O33" s="5" t="n">
         <v>1</v>
@@ -8096,13 +8096,13 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="R33" s="11" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="S33" s="6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34">
@@ -8137,10 +8137,10 @@
         <v>10</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K34" s="5" t="n">
         <v>12</v>
@@ -8149,10 +8149,10 @@
         <v>12</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N34" s="11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O34" s="5" t="n">
         <v>0</v>
@@ -8161,13 +8161,13 @@
         <v>0</v>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="R34" s="11" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="S34" s="6" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35">
@@ -8202,10 +8202,10 @@
         <v>10</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K35" s="5" t="n">
         <v>12</v>
@@ -8214,10 +8214,10 @@
         <v>12</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N35" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O35" s="5" t="n">
         <v>2</v>
@@ -8226,13 +8226,13 @@
         <v>2</v>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R35" s="11" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="S35" s="6" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
@@ -8267,10 +8267,10 @@
         <v>10</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>12</v>
@@ -8279,25 +8279,25 @@
         <v>12</v>
       </c>
       <c r="M36" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="N36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="N36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="R36" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S36" s="6" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37">
@@ -8332,10 +8332,10 @@
         <v>10</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="K37" s="5" t="n">
         <v>12</v>
@@ -8344,7 +8344,7 @@
         <v>12</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N37" s="11" t="n">
         <v>0</v>
@@ -8356,13 +8356,13 @@
         <v>1</v>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="R37" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
@@ -8397,10 +8397,10 @@
         <v>10</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K38" s="5" t="n">
         <v>12</v>
@@ -8409,10 +8409,10 @@
         <v>12</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N38" s="11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O38" s="5" t="n">
         <v>0</v>
@@ -8421,13 +8421,13 @@
         <v>0</v>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R38" s="11" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S38" s="6" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39">
@@ -8462,10 +8462,10 @@
         <v>10</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K39" s="5" t="n">
         <v>12</v>
@@ -8474,10 +8474,10 @@
         <v>12</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" s="5" t="n">
         <v>0</v>
@@ -8486,13 +8486,13 @@
         <v>0</v>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="R39" s="11" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S39" s="6" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40">
@@ -8527,10 +8527,10 @@
         <v>10</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J40" s="11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K40" s="5" t="n">
         <v>11</v>
@@ -8539,10 +8539,10 @@
         <v>11</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O40" s="5" t="n">
         <v>1</v>
@@ -8551,13 +8551,13 @@
         <v>1</v>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S40" s="6" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -8592,10 +8592,10 @@
         <v>9</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K41" s="5" t="n">
         <v>11</v>
@@ -8604,7 +8604,7 @@
         <v>11</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N41" s="11" t="n">
         <v>0</v>
@@ -8616,13 +8616,13 @@
         <v>0</v>
       </c>
       <c r="Q41" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="R41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" s="6" t="n">
         <v>35</v>
-      </c>
-      <c r="R41" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="S41" s="6" t="n">
-        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -8657,10 +8657,10 @@
         <v>8</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K42" s="5" t="n">
         <v>10</v>
@@ -8669,10 +8669,10 @@
         <v>10</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N42" s="11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O42" s="5" t="n">
         <v>0</v>
@@ -8681,13 +8681,13 @@
         <v>0</v>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="R42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S42" s="6" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43">
@@ -8722,10 +8722,10 @@
         <v>8</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K43" s="5" t="n">
         <v>10</v>
@@ -8746,13 +8746,13 @@
         <v>0</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="R43" s="11" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="S43" s="6" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44">
@@ -8787,10 +8787,10 @@
         <v>8</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K44" s="5" t="n">
         <v>10</v>
@@ -8799,10 +8799,10 @@
         <v>10</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N44" s="11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O44" s="5" t="n">
         <v>0</v>
@@ -8811,13 +8811,13 @@
         <v>0</v>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R44" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S44" s="6" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45">
@@ -8852,10 +8852,10 @@
         <v>8</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K45" s="5" t="n">
         <v>9</v>
@@ -8864,10 +8864,10 @@
         <v>9</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N45" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O45" s="5" t="n">
         <v>0</v>
@@ -8876,13 +8876,13 @@
         <v>0</v>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="R45" s="11" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="S45" s="6" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46">
@@ -8917,10 +8917,10 @@
         <v>8</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K46" s="5" t="n">
         <v>9</v>
@@ -8929,7 +8929,7 @@
         <v>9</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N46" s="11" t="n">
         <v>0</v>
@@ -8941,13 +8941,13 @@
         <v>0</v>
       </c>
       <c r="Q46" s="5" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="R46" s="11" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="S46" s="6" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47">
@@ -8982,10 +8982,10 @@
         <v>7</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="K47" s="5" t="n">
         <v>9</v>
@@ -8994,10 +8994,10 @@
         <v>9</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N47" s="11" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O47" s="5" t="n">
         <v>0</v>
@@ -9006,13 +9006,13 @@
         <v>0</v>
       </c>
       <c r="Q47" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R47" s="11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S47" s="6" t="n">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48">
@@ -9047,10 +9047,10 @@
         <v>7</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K48" s="5" t="n">
         <v>9</v>
@@ -9059,10 +9059,10 @@
         <v>9</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N48" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O48" s="5" t="n">
         <v>0</v>
@@ -9071,13 +9071,13 @@
         <v>0</v>
       </c>
       <c r="Q48" s="5" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="R48" s="11" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="S48" s="6" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -9112,10 +9112,10 @@
         <v>7</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K49" s="5" t="n">
         <v>8</v>
@@ -9124,7 +9124,7 @@
         <v>8</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N49" s="11" t="n">
         <v>0</v>
@@ -9136,13 +9136,13 @@
         <v>0</v>
       </c>
       <c r="Q49" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R49" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S49" s="6" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
@@ -9177,10 +9177,10 @@
         <v>7</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J50" s="11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K50" s="5" t="n">
         <v>8</v>
@@ -9189,10 +9189,10 @@
         <v>8</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N50" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O50" s="5" t="n">
         <v>0</v>
@@ -9201,13 +9201,13 @@
         <v>0</v>
       </c>
       <c r="Q50" s="5" t="n">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="R50" s="11" t="n">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="S50" s="6" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51">
@@ -9242,10 +9242,10 @@
         <v>6</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K51" s="5" t="n">
         <v>8</v>
@@ -9254,10 +9254,10 @@
         <v>8</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N51" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="5" t="n">
         <v>0</v>
@@ -9266,13 +9266,13 @@
         <v>0</v>
       </c>
       <c r="Q51" s="5" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="R51" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S51" s="6" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
@@ -9307,10 +9307,10 @@
         <v>6</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J52" s="11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K52" s="5" t="n">
         <v>7</v>
@@ -9319,7 +9319,7 @@
         <v>7</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="N52" s="11" t="n">
         <v>0</v>
@@ -9331,13 +9331,13 @@
         <v>0</v>
       </c>
       <c r="Q52" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R52" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S52" s="6" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
@@ -9372,10 +9372,10 @@
         <v>6</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K53" s="5" t="n">
         <v>7</v>
@@ -9384,7 +9384,7 @@
         <v>7</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N53" s="11" t="n">
         <v>0</v>
@@ -9396,13 +9396,13 @@
         <v>0</v>
       </c>
       <c r="Q53" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R53" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S53" s="6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -9437,10 +9437,10 @@
         <v>6</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K54" s="5" t="n">
         <v>7</v>
@@ -9449,7 +9449,7 @@
         <v>7</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N54" s="11" t="n">
         <v>0</v>
@@ -9461,13 +9461,13 @@
         <v>0</v>
       </c>
       <c r="Q54" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R54" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S54" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -9502,10 +9502,10 @@
         <v>6</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K55" s="5" t="n">
         <v>7</v>
@@ -9514,7 +9514,7 @@
         <v>7</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N55" s="11" t="n">
         <v>0</v>
@@ -9526,13 +9526,13 @@
         <v>0</v>
       </c>
       <c r="Q55" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R55" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S55" s="6" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -9567,10 +9567,10 @@
         <v>6</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J56" s="11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K56" s="5" t="n">
         <v>7</v>
@@ -9579,10 +9579,10 @@
         <v>7</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N56" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O56" s="5" t="n">
         <v>1</v>
@@ -9591,13 +9591,13 @@
         <v>1</v>
       </c>
       <c r="Q56" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R56" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S56" s="6" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57">
@@ -9632,10 +9632,10 @@
         <v>6</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J57" s="11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K57" s="5" t="n">
         <v>7</v>
@@ -9644,10 +9644,10 @@
         <v>7</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="N57" s="11" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="O57" s="5" t="n">
         <v>0</v>
@@ -9656,13 +9656,13 @@
         <v>0</v>
       </c>
       <c r="Q57" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R57" s="11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S57" s="6" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58">
@@ -9697,10 +9697,10 @@
         <v>6</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K58" s="5" t="n">
         <v>7</v>
@@ -9709,10 +9709,10 @@
         <v>7</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N58" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O58" s="5" t="n">
         <v>0</v>
@@ -9721,13 +9721,13 @@
         <v>0</v>
       </c>
       <c r="Q58" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R58" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S58" s="6" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59">
@@ -9762,10 +9762,10 @@
         <v>5</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K59" s="5" t="n">
         <v>6</v>
@@ -9774,10 +9774,10 @@
         <v>6</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N59" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O59" s="5" t="n">
         <v>0</v>
@@ -9786,13 +9786,13 @@
         <v>0</v>
       </c>
       <c r="Q59" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R59" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S59" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
@@ -9827,10 +9827,10 @@
         <v>5</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K60" s="5" t="n">
         <v>6</v>
@@ -9839,7 +9839,7 @@
         <v>6</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N60" s="11" t="n">
         <v>0</v>
@@ -9851,13 +9851,13 @@
         <v>0</v>
       </c>
       <c r="Q60" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R60" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S60" s="6" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
@@ -9892,10 +9892,10 @@
         <v>5</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K61" s="5" t="n">
         <v>6</v>
@@ -9904,7 +9904,7 @@
         <v>6</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N61" s="11" t="n">
         <v>0</v>
@@ -9916,13 +9916,13 @@
         <v>0</v>
       </c>
       <c r="Q61" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R61" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S61" s="6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
@@ -9957,10 +9957,10 @@
         <v>5</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J62" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K62" s="5" t="n">
         <v>5</v>
@@ -9969,7 +9969,7 @@
         <v>5</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N62" s="11" t="n">
         <v>0</v>
@@ -9981,13 +9981,13 @@
         <v>1</v>
       </c>
       <c r="Q62" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R62" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S62" s="6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63">
@@ -10022,10 +10022,10 @@
         <v>4</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J63" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K63" s="5" t="n">
         <v>5</v>
@@ -10034,25 +10034,25 @@
         <v>5</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N63" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="O63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="R63" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S63" s="6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64">
@@ -10087,10 +10087,10 @@
         <v>4</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J64" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K64" s="5" t="n">
         <v>5</v>
@@ -10117,7 +10117,7 @@
         <v>7</v>
       </c>
       <c r="S64" s="6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
@@ -10152,10 +10152,10 @@
         <v>4</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J65" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K65" s="5" t="n">
         <v>5</v>
@@ -10164,7 +10164,7 @@
         <v>5</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N65" s="11" t="n">
         <v>0</v>
@@ -10176,13 +10176,13 @@
         <v>0</v>
       </c>
       <c r="Q65" s="5" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="R65" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S65" s="6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66">
@@ -10217,10 +10217,10 @@
         <v>4</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J66" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K66" s="5" t="n">
         <v>5</v>
@@ -10229,10 +10229,10 @@
         <v>5</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N66" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O66" s="5" t="n">
         <v>0</v>
@@ -10241,13 +10241,13 @@
         <v>0</v>
       </c>
       <c r="Q66" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R66" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S66" s="6" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67">
@@ -10282,10 +10282,10 @@
         <v>4</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J67" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K67" s="5" t="n">
         <v>5</v>
@@ -10294,10 +10294,10 @@
         <v>5</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N67" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O67" s="5" t="n">
         <v>0</v>
@@ -10306,13 +10306,13 @@
         <v>0</v>
       </c>
       <c r="Q67" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R67" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S67" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68">
@@ -10347,10 +10347,10 @@
         <v>4</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J68" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K68" s="5" t="n">
         <v>5</v>
@@ -10359,7 +10359,7 @@
         <v>5</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N68" s="11" t="n">
         <v>0</v>
@@ -10371,13 +10371,13 @@
         <v>0</v>
       </c>
       <c r="Q68" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R68" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S68" s="6" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
@@ -10412,10 +10412,10 @@
         <v>4</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J69" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K69" s="5" t="n">
         <v>5</v>
@@ -10424,10 +10424,10 @@
         <v>5</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N69" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O69" s="5" t="n">
         <v>2</v>
@@ -10442,7 +10442,7 @@
         <v>0</v>
       </c>
       <c r="S69" s="6" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
@@ -10477,10 +10477,10 @@
         <v>4</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J70" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K70" s="5" t="n">
         <v>5</v>
@@ -10489,7 +10489,7 @@
         <v>5</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N70" s="11" t="n">
         <v>0</v>
@@ -10501,13 +10501,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="R70" s="11" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="S70" s="6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71">
@@ -10542,10 +10542,10 @@
         <v>4</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J71" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K71" s="5" t="n">
         <v>4</v>
@@ -10554,10 +10554,10 @@
         <v>4</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N71" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O71" s="5" t="n">
         <v>0</v>
@@ -10566,13 +10566,13 @@
         <v>0</v>
       </c>
       <c r="Q71" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R71" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S71" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
@@ -10607,10 +10607,10 @@
         <v>4</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J72" s="11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K72" s="5" t="n">
         <v>4</v>
@@ -10619,10 +10619,10 @@
         <v>4</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N72" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O72" s="5" t="n">
         <v>0</v>
@@ -10631,13 +10631,13 @@
         <v>0</v>
       </c>
       <c r="Q72" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R72" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S72" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
@@ -10684,10 +10684,10 @@
         <v>4</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N73" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O73" s="5" t="n">
         <v>0</v>
@@ -10696,13 +10696,13 @@
         <v>0</v>
       </c>
       <c r="Q73" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R73" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S73" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
@@ -10737,10 +10737,10 @@
         <v>3</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J74" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K74" s="5" t="n">
         <v>4</v>
@@ -10749,25 +10749,25 @@
         <v>4</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N74" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="O74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="R74" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S74" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75">
@@ -10802,10 +10802,10 @@
         <v>3</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J75" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K75" s="5" t="n">
         <v>4</v>
@@ -10814,10 +10814,10 @@
         <v>4</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N75" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O75" s="5" t="n">
         <v>0</v>
@@ -10826,13 +10826,13 @@
         <v>0</v>
       </c>
       <c r="Q75" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R75" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S75" s="6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
@@ -10867,10 +10867,10 @@
         <v>3</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J76" s="11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K76" s="5" t="n">
         <v>4</v>
@@ -10879,10 +10879,10 @@
         <v>4</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N76" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O76" s="5" t="n">
         <v>0</v>
@@ -10891,13 +10891,13 @@
         <v>0</v>
       </c>
       <c r="Q76" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R76" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S76" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77">
@@ -10932,10 +10932,10 @@
         <v>3</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J77" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K77" s="5" t="n">
         <v>4</v>
@@ -10944,25 +10944,25 @@
         <v>4</v>
       </c>
       <c r="M77" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="N77" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="R77" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S77" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
@@ -10997,10 +10997,10 @@
         <v>3</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J78" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K78" s="5" t="n">
         <v>4</v>
@@ -11009,25 +11009,25 @@
         <v>4</v>
       </c>
       <c r="M78" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="N78" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="R78" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S78" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79">
@@ -11062,10 +11062,10 @@
         <v>3</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J79" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K79" s="5" t="n">
         <v>4</v>
@@ -11074,10 +11074,10 @@
         <v>4</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N79" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O79" s="5" t="n">
         <v>0</v>
@@ -11086,13 +11086,13 @@
         <v>0</v>
       </c>
       <c r="Q79" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R79" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S79" s="6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80">
@@ -11127,10 +11127,10 @@
         <v>3</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J80" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K80" s="5" t="n">
         <v>3</v>
@@ -11139,7 +11139,7 @@
         <v>3</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N80" s="11" t="n">
         <v>0</v>
@@ -11151,13 +11151,13 @@
         <v>0</v>
       </c>
       <c r="Q80" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R80" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S80" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81">
@@ -11192,10 +11192,10 @@
         <v>3</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J81" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K81" s="5" t="n">
         <v>3</v>
@@ -11204,10 +11204,10 @@
         <v>3</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N81" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O81" s="5" t="n">
         <v>0</v>
@@ -11216,13 +11216,13 @@
         <v>0</v>
       </c>
       <c r="Q81" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R81" s="11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S81" s="6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82">
@@ -11257,10 +11257,10 @@
         <v>3</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J82" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K82" s="5" t="n">
         <v>3</v>
@@ -11269,25 +11269,25 @@
         <v>3</v>
       </c>
       <c r="M82" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="N82" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="R82" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S82" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -11322,10 +11322,10 @@
         <v>3</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J83" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K83" s="5" t="n">
         <v>3</v>
@@ -11334,10 +11334,10 @@
         <v>3</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N83" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O83" s="5" t="n">
         <v>1</v>
@@ -11346,13 +11346,13 @@
         <v>1</v>
       </c>
       <c r="Q83" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R83" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S83" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84">
@@ -11387,10 +11387,10 @@
         <v>3</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J84" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K84" s="5" t="n">
         <v>3</v>
@@ -11399,10 +11399,10 @@
         <v>3</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N84" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O84" s="5" t="n">
         <v>0</v>
@@ -11411,13 +11411,13 @@
         <v>0</v>
       </c>
       <c r="Q84" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R84" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S84" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85">
@@ -11452,10 +11452,10 @@
         <v>3</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K85" s="5" t="n">
         <v>3</v>
@@ -11464,7 +11464,7 @@
         <v>3</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N85" s="11" t="n">
         <v>0</v>
@@ -11482,7 +11482,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
@@ -11517,10 +11517,10 @@
         <v>3</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K86" s="5" t="n">
         <v>3</v>
@@ -11529,7 +11529,7 @@
         <v>3</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N86" s="11" t="n">
         <v>0</v>
@@ -11541,13 +11541,13 @@
         <v>0</v>
       </c>
       <c r="Q86" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R86" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S86" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
@@ -11582,10 +11582,10 @@
         <v>2</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K87" s="5" t="n">
         <v>3</v>
@@ -11594,10 +11594,10 @@
         <v>3</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N87" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O87" s="5" t="n">
         <v>0</v>
@@ -11606,13 +11606,13 @@
         <v>0</v>
       </c>
       <c r="Q87" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R87" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S87" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
@@ -11647,10 +11647,10 @@
         <v>2</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J88" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K88" s="5" t="n">
         <v>3</v>
@@ -11659,22 +11659,22 @@
         <v>3</v>
       </c>
       <c r="M88" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="N88" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="R88" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S88" s="6" t="n">
         <v>13</v>
@@ -11712,10 +11712,10 @@
         <v>2</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J89" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K89" s="5" t="n">
         <v>3</v>
@@ -11724,10 +11724,10 @@
         <v>3</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N89" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O89" s="5" t="n">
         <v>0</v>
@@ -11736,13 +11736,13 @@
         <v>0</v>
       </c>
       <c r="Q89" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R89" s="11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S89" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90">
@@ -11777,10 +11777,10 @@
         <v>2</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J90" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K90" s="5" t="n">
         <v>3</v>
@@ -11789,7 +11789,7 @@
         <v>3</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N90" s="11" t="n">
         <v>0</v>
@@ -11801,13 +11801,13 @@
         <v>0</v>
       </c>
       <c r="Q90" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R90" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S90" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
@@ -11842,10 +11842,10 @@
         <v>2</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J91" s="11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K91" s="5" t="n">
         <v>3</v>
@@ -11854,10 +11854,10 @@
         <v>3</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N91" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O91" s="5" t="n">
         <v>0</v>
@@ -11866,13 +11866,13 @@
         <v>0</v>
       </c>
       <c r="Q91" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R91" s="11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S91" s="6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
@@ -11907,10 +11907,10 @@
         <v>2</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J92" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K92" s="5" t="n">
         <v>3</v>
@@ -11919,10 +11919,10 @@
         <v>3</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N92" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O92" s="5" t="n">
         <v>0</v>
@@ -11931,13 +11931,13 @@
         <v>0</v>
       </c>
       <c r="Q92" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R92" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S92" s="6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93">
@@ -11972,10 +11972,10 @@
         <v>2</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J93" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K93" s="5" t="n">
         <v>3</v>
@@ -11996,13 +11996,13 @@
         <v>0</v>
       </c>
       <c r="Q93" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R93" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S93" s="6" t="n">
         <v>11</v>
-      </c>
-      <c r="R93" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="S93" s="6" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="94">
@@ -12037,10 +12037,10 @@
         <v>2</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J94" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K94" s="5" t="n">
         <v>2</v>
@@ -12049,7 +12049,7 @@
         <v>2</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N94" s="11" t="n">
         <v>0</v>
@@ -12067,7 +12067,7 @@
         <v>0</v>
       </c>
       <c r="S94" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -12114,25 +12114,25 @@
         <v>2</v>
       </c>
       <c r="M95" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="6" t="n">
         <v>7</v>
-      </c>
-      <c r="N95" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="R95" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S95" s="6" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="96">
@@ -12179,10 +12179,10 @@
         <v>2</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N96" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O96" s="5" t="n">
         <v>0</v>
@@ -12191,13 +12191,13 @@
         <v>0</v>
       </c>
       <c r="Q96" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R96" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S96" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
@@ -12232,10 +12232,10 @@
         <v>2</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J97" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K97" s="5" t="n">
         <v>2</v>
@@ -12244,10 +12244,10 @@
         <v>2</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N97" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" s="5" t="n">
         <v>1</v>
@@ -12256,7 +12256,7 @@
         <v>1</v>
       </c>
       <c r="Q97" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R97" s="11" t="n">
         <v>0</v>
@@ -12309,7 +12309,7 @@
         <v>2</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N98" s="11" t="n">
         <v>0</v>
@@ -12321,13 +12321,13 @@
         <v>0</v>
       </c>
       <c r="Q98" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R98" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S98" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99">
@@ -12362,10 +12362,10 @@
         <v>1</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J99" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K99" s="5" t="n">
         <v>2</v>
@@ -12374,10 +12374,10 @@
         <v>2</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N99" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" s="5" t="n">
         <v>0</v>
@@ -12386,13 +12386,13 @@
         <v>0</v>
       </c>
       <c r="Q99" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R99" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S99" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
@@ -12427,10 +12427,10 @@
         <v>1</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J100" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K100" s="5" t="n">
         <v>2</v>
@@ -12439,7 +12439,7 @@
         <v>2</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N100" s="11" t="n">
         <v>0</v>
@@ -12451,13 +12451,13 @@
         <v>0</v>
       </c>
       <c r="Q100" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R100" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S100" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -12504,7 +12504,7 @@
         <v>2</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N101" s="11" t="n">
         <v>0</v>
@@ -12516,7 +12516,7 @@
         <v>0</v>
       </c>
       <c r="Q101" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R101" s="11" t="n">
         <v>0</v>
@@ -12557,10 +12557,10 @@
         <v>1</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J102" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K102" s="5" t="n">
         <v>2</v>
@@ -12569,10 +12569,10 @@
         <v>2</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N102" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O102" s="5" t="n">
         <v>0</v>
@@ -12622,10 +12622,10 @@
         <v>1</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J103" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K103" s="5" t="n">
         <v>2</v>
@@ -12646,13 +12646,13 @@
         <v>0</v>
       </c>
       <c r="Q103" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R103" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S103" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104">
@@ -12687,10 +12687,10 @@
         <v>1</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J104" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K104" s="5" t="n">
         <v>2</v>
@@ -12699,25 +12699,25 @@
         <v>2</v>
       </c>
       <c r="M104" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N104" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="N104" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="R104" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S104" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -12752,10 +12752,10 @@
         <v>1</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J105" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K105" s="5" t="n">
         <v>1</v>
@@ -12764,10 +12764,10 @@
         <v>1</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N105" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105" s="5" t="n">
         <v>0</v>
@@ -12776,13 +12776,13 @@
         <v>0</v>
       </c>
       <c r="Q105" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R105" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S105" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
@@ -12817,10 +12817,10 @@
         <v>1</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J106" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K106" s="5" t="n">
         <v>1</v>
@@ -12829,10 +12829,10 @@
         <v>1</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N106" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O106" s="5" t="n">
         <v>0</v>
@@ -12847,7 +12847,7 @@
         <v>2</v>
       </c>
       <c r="S106" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -12882,10 +12882,10 @@
         <v>1</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J107" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K107" s="5" t="n">
         <v>1</v>
@@ -12894,10 +12894,10 @@
         <v>1</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N107" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O107" s="5" t="n">
         <v>0</v>
@@ -12906,13 +12906,13 @@
         <v>0</v>
       </c>
       <c r="Q107" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R107" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S107" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -12947,10 +12947,10 @@
         <v>1</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J108" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K108" s="5" t="n">
         <v>1</v>
@@ -12959,7 +12959,7 @@
         <v>1</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N108" s="11" t="n">
         <v>0</v>
@@ -12977,7 +12977,7 @@
         <v>0</v>
       </c>
       <c r="S108" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
@@ -13012,10 +13012,10 @@
         <v>1</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K109" s="5" t="n">
         <v>1</v>
@@ -13024,10 +13024,10 @@
         <v>1</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N109" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O109" s="5" t="n">
         <v>0</v>
@@ -13036,13 +13036,13 @@
         <v>0</v>
       </c>
       <c r="Q109" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R109" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S109" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110">
@@ -13077,10 +13077,10 @@
         <v>1</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K110" s="5" t="n">
         <v>1</v>
@@ -13101,13 +13101,13 @@
         <v>1</v>
       </c>
       <c r="Q110" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R110" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S110" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
@@ -13154,10 +13154,10 @@
         <v>1</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N111" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" s="5" t="n">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         <v>0</v>
       </c>
       <c r="S111" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -13207,10 +13207,10 @@
         <v>1</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" s="5" t="n">
         <v>1</v>
@@ -13219,10 +13219,10 @@
         <v>1</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N112" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" s="5" t="n">
         <v>0</v>
@@ -13231,13 +13231,13 @@
         <v>0</v>
       </c>
       <c r="Q112" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R112" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S112" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113">
@@ -13284,7 +13284,7 @@
         <v>1</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N113" s="11" t="n">
         <v>0</v>
@@ -13296,7 +13296,7 @@
         <v>0</v>
       </c>
       <c r="Q113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="11" t="n">
         <v>0</v>
@@ -13337,10 +13337,10 @@
         <v>1</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J114" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K114" s="5" t="n">
         <v>1</v>
@@ -13349,10 +13349,10 @@
         <v>1</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N114" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" s="5" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>0</v>
       </c>
       <c r="Q114" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R114" s="11" t="n">
         <v>0</v>
@@ -13402,10 +13402,10 @@
         <v>1</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K115" s="5" t="n">
         <v>1</v>
@@ -13426,13 +13426,13 @@
         <v>0</v>
       </c>
       <c r="Q115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R115" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S115" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
@@ -13467,10 +13467,10 @@
         <v>1</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K116" s="5" t="n">
         <v>1</v>
@@ -13491,10 +13491,10 @@
         <v>0</v>
       </c>
       <c r="Q116" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R116" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S116" s="6" t="n">
         <v>3</v>
@@ -13544,7 +13544,7 @@
         <v>1</v>
       </c>
       <c r="M117" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N117" s="11" t="n">
         <v>0</v>
@@ -13556,7 +13556,7 @@
         <v>0</v>
       </c>
       <c r="Q117" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R117" s="11" t="n">
         <v>0</v>
@@ -13597,37 +13597,37 @@
         <v>1</v>
       </c>
       <c r="I118" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R118" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S118" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="J118" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K118" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" s="6" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="119">
@@ -13674,7 +13674,7 @@
         <v>1</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N119" s="11" t="n">
         <v>0</v>
@@ -13727,10 +13727,10 @@
         <v>0</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K120" s="5" t="n">
         <v>1</v>
@@ -13739,25 +13739,25 @@
         <v>1</v>
       </c>
       <c r="M120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R120" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S120" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="N120" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -13816,7 +13816,7 @@
         <v>0</v>
       </c>
       <c r="Q121" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R121" s="11" t="n">
         <v>0</v>
@@ -13857,10 +13857,10 @@
         <v>0</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122" s="5" t="n">
         <v>1</v>
@@ -13881,13 +13881,13 @@
         <v>0</v>
       </c>
       <c r="Q122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S122" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -13946,13 +13946,13 @@
         <v>0</v>
       </c>
       <c r="Q123" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R123" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S123" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -13999,10 +13999,10 @@
         <v>0</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N124" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O124" s="5" t="n">
         <v>0</v>
@@ -14011,13 +14011,13 @@
         <v>0</v>
       </c>
       <c r="Q124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R124" s="11" t="n">
         <v>0</v>
       </c>
       <c r="S124" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -14052,10 +14052,10 @@
         <v>0</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125" s="5" t="n">
         <v>0</v>
@@ -14082,7 +14082,7 @@
         <v>0</v>
       </c>
       <c r="S125" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -14117,10 +14117,10 @@
         <v>0</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" s="5" t="n">
         <v>0</v>
@@ -14141,13 +14141,13 @@
         <v>0</v>
       </c>
       <c r="Q126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S126" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -14194,7 +14194,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N127" s="11" t="n">
         <v>0</v>
@@ -14259,7 +14259,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N128" s="11" t="n">
         <v>0</v>
@@ -14312,10 +14312,10 @@
         <v>0</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" s="5" t="n">
         <v>0</v>
@@ -14324,7 +14324,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N129" s="11" t="n">
         <v>0</v>
@@ -14342,7 +14342,7 @@
         <v>0</v>
       </c>
       <c r="S129" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -14389,7 +14389,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N130" s="11" t="n">
         <v>0</v>
@@ -14584,10 +14584,10 @@
         <v>0</v>
       </c>
       <c r="M133" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N133" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O133" s="5" t="n">
         <v>0</v>
@@ -14602,7 +14602,7 @@
         <v>0</v>
       </c>
       <c r="S133" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -14637,10 +14637,10 @@
         <v>0</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J134" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K134" s="5" t="n">
         <v>0</v>
@@ -14667,7 +14667,7 @@
         <v>0</v>
       </c>
       <c r="S134" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -14702,10 +14702,10 @@
         <v>0</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K135" s="5" t="n">
         <v>0</v>
@@ -14732,7 +14732,7 @@
         <v>0</v>
       </c>
       <c r="S135" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="Q140" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R140" s="11" t="n">
         <v>0</v>
@@ -15246,13 +15246,13 @@
         <v>0</v>
       </c>
       <c r="Q143" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R143" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S143" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -15268,10 +15268,10 @@
         <v>1627</v>
       </c>
       <c r="I144" s="13" t="n">
-        <v>3051</v>
+        <v>2432</v>
       </c>
       <c r="J144" s="13" t="n">
-        <v>3051</v>
+        <v>2432</v>
       </c>
       <c r="K144" s="13" t="n">
         <v>1955</v>
@@ -15280,10 +15280,10 @@
         <v>1955</v>
       </c>
       <c r="M144" s="13" t="n">
-        <v>2656</v>
+        <v>1307</v>
       </c>
       <c r="N144" s="13" t="n">
-        <v>1794</v>
+        <v>640</v>
       </c>
       <c r="O144" s="13" t="n">
         <v>66</v>
@@ -15292,13 +15292,13 @@
         <v>61</v>
       </c>
       <c r="Q144" s="13" t="n">
-        <v>2749</v>
+        <v>2703</v>
       </c>
       <c r="R144" s="13" t="n">
-        <v>1660</v>
+        <v>1542</v>
       </c>
       <c r="S144" s="13" t="n">
-        <v>10148</v>
+        <v>8257</v>
       </c>
     </row>
   </sheetData>
@@ -15327,20 +15327,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Итоги поставки по складам</t>
+          <t>Итоги поставки по складам (спрос = федеральный округ)</t>
         </is>
       </c>
     </row>
@@ -15352,20 +15353,25 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>Фед. округ</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
           <t>Спрос/мес,шт</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Текущий остаток,шт</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>К поставке,шт</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
@@ -15377,18 +15383,23 @@
           <t>Питер</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Северо-Западный</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>1627</v>
       </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="n">
         <v>1627</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>нет своего запаса — спрос Северо-Западного ФО (8,4%)</t>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>пустой склад — весь спрос округа</t>
         </is>
       </c>
     </row>
@@ -15398,18 +15409,23 @@
           <t>Краснодар</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>3051</v>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Южный</t>
+        </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>3051</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>склад пустой — везём весь спрос</t>
+        <v>2432</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>2432</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>пустой склад — весь спрос округа</t>
         </is>
       </c>
     </row>
@@ -15419,18 +15435,23 @@
           <t>Новосибирск</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Сибирский</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
         <v>1955</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11" t="n">
         <v>1955</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>нет истории — спрос Сибирского ФО (10,1%)</t>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>пустой склад — весь спрос округа</t>
         </is>
       </c>
     </row>
@@ -15440,16 +15461,21 @@
           <t>Екатеринбург</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>2656</v>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Уральский</t>
+        </is>
       </c>
       <c r="C7" s="5" t="n">
+        <v>1307</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>1759</v>
       </c>
-      <c r="D7" s="11" t="n">
-        <v>1794</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>есть остаток, довозим разницу</t>
         </is>
@@ -15461,18 +15487,23 @@
           <t>Владимир</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Центральный (факт)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="D8" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="E8" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>малый спрос</t>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>ЦФО обслуживают Коледино/Тула — берём факт склада</t>
         </is>
       </c>
     </row>
@@ -15482,16 +15513,21 @@
           <t>Казань</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>2749</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Приволжский</t>
+        </is>
       </c>
       <c r="C9" s="5" t="n">
+        <v>2703</v>
+      </c>
+      <c r="D9" s="5" t="n">
         <v>3497</v>
       </c>
-      <c r="D9" s="11" t="n">
-        <v>1660</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="11" t="n">
+        <v>1542</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>есть остаток, довозим разницу</t>
         </is>
@@ -15503,16 +15539,17 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
-        <v>12104</v>
-      </c>
+      <c r="B10" s="14" t="inlineStr"/>
       <c r="C10" s="13" t="n">
+        <v>10090</v>
+      </c>
+      <c r="D10" s="13" t="n">
         <v>5267</v>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>10148</v>
-      </c>
-      <c r="E10" s="14" t="inlineStr"/>
+      <c r="E10" s="13" t="n">
+        <v>8257</v>
+      </c>
+      <c r="F10" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
